--- a/data_extactor/batch_10_fa/trimmed/batch_0043_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0043_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پرستاران بالینی پیشرفته (Nurse Practitioners) | کارشناسان فوریت‌های پزشکی (پارامدیک) | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پرستاران بالینی پیشرفته | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | علوم پایه</t>
+          <t>گوش دادن فعال | درک مطلب | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات | زیست‌شناسی | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | شیمی | خدمات مشتری و شخصی | ریاضیات | زیست‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | پرستاران بخش مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | هوشبَران و پرستاران بیهوشی | دستیاران پزشک | کارشناسان مراقبت‌های تنفسی | کارشناسان اتاق عمل (تکنولوژیست‌های جراحی)</t>
+          <t>متخصصان بیهوشی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پرستاران بیهوشی | دستیاران پزشک | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زیست‌شناسی | مدیریت و امور اداری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | زیست‌شناسی | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | حساسیت به مسئله | درک شفاهی | بیان شفاهی | دید نزدیک</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | حساسیت به مسئله | درک شفاهی | بیان شفاهی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان کایروپراکتیک (درمان دستی) | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | دستیاران پزشک و پیراپزشکان بالینی | جراحان ارتوپدی (غیر از کودکان) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی</t>
+          <t>کایروپراکتورها / متخصصان درمان دستی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | آموزش و تدریس | زیست‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان توانبخشی و جهت‌یابی نابینایان و کم‌بینایان | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی</t>
+          <t>متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | حمل‌ونقل و ترابری | خدمات مشتریان و خدمات فردی | درمان و مشاوره | ایمنی و امنیت عمومی</t>
+          <t>آموزش و پرورش | روان‌شناسی | حمل و نقل | خدمات مشتری و شخصی | درمان و مشاوره | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مربیان تربیت بدنی تطبیقی و استثنایی | کاردرمانگران | دستیاران کاردرمانی | فیزیوتراپیست‌ها | مشاوران توانبخشی | آموزگاران آموزش استثنایی دوره ابتدایی | آسیب‌شناسان گفتار و زبان (گفتاردرمانگران)</t>
+          <t>متخصصان تربیت بدنی انطباقی | کاردرمانگران | کاردان‌های کاردرمانی | فیزیوتراپیست‌ها | مشاوران توانبخشی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | پزشکی و دندان‌پزشکی | روان‌شناسی | آموزش و تدریس | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | پزشکی و دندان‌پزشکی | روان‌شناسی | آموزش و پرورش | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کاردرمانگران | جراحان ارتوپدی (غیر از کودکان) | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی</t>
+          <t>کاردرمانگران | جراحان ارتوپدی، غیر از اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | کارشناسان تفریح‌درمانی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | فیزیک | ریاضیات | رایانه و الکترونیک | زیست‌شناسی</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | فیزیک | ریاضیات | رایانه و الکترونیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سونوگرافیست‌ها و کارشناسان سونوگرافی تشخیصی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دوزیمتریست‌های پرتودرمانی | کارشناسان پزشکی هسته‌ای | کارشناسان و تکنسین‌های رادیولوژی و پرتو‌نگاری | پزشکان رادیولوژیست | دستیاران جراحی</t>
+          <t>سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>هنردرمانگران | ماساژدرمانگران | موسیقی‌درمانگران | کاردرمانگران | دستیاران کاردرمانی | فیزیوتراپیست‌ها | مشاوران توانبخشی</t>
+          <t>هنر‌درمانگران | ماساژدرمانگران | موسیقی‌درمانگران | کاردرمانگران | کاردان‌های کاردرمانی | فیزیوتراپیست‌ها | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم پایه</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | آموزش و تدریس | زیست‌شناسی | رایانه و الکترونیک | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | زیست‌شناسی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | پرستاران بخش مراقبت‌های ویژه (ICU) | هوشبَران و پرستاران بیهوشی | کارشناسان فوریت‌های پزشکی (پارامدیک) | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | پرستاران مراقبت‌های ویژه | پرستاران بیهوشی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان (ادیولوژیست‌ها) | روان‌شناسان بالینی و مشاوره | کارشناسان توانبخشی و جهت‌یابی نابینایان و کم‌بینایان | کاردرمانگران | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی | دستیاران گفتاردرمانی</t>
+          <t>شنوایی‌شناسان | روان‌شناسان بالینی و مشاوران سلامت روان | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | کاردرمانگران | فیزیوتراپیست‌ها | کارشناسان تفریح‌درمانی | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
